--- a/business_surveys/038_election_contexts_survey--business_surveys.xlsx
+++ b/business_surveys/038_election_contexts_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'news'}</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'News'}</t>
+          <t>News</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6,_'text':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6, 'text': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'not_fair'}</t>
+          <t>not_fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Not Fair'}</t>
+          <t>Not Fair</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
